--- a/Caddie POC - Result Validation.xlsx
+++ b/Caddie POC - Result Validation.xlsx
@@ -14640,27 +14640,148 @@
       </c>
       <c r="D118" s="21" t="inlineStr">
         <is>
+          <t>## Result
+No bills were generated in the **last 7 days** in the available billing data.
+Supporting figures:
+| Metric | Value |
+|---|---:|
+| Bill rows in the last 7 days | 0 |
+| Distinct CANs billed in the last 7 days | 0 |
+| Requested window start | 2026-05-13 |
+| Requested window end | 2026-05-20 |
+This happens because the billing source `MV_BILLING_PAYMENT_HISTORY` currently contains data only from `2025-01-01` to `2025-06-30`, so there are no bill rows at all in the requested last-7-days window relative to the current system date.</t>
+        </is>
+      </c>
+      <c r="E118" s="22" t="inlineStr">
+        <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E118" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
       <c r="F118" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>## Context Needed for Quicker Response
+### Canonical Objects
+- **Primary billing object:** `CTLHMWSSBTMP.MV_BILLING_PAYMENT_HISTORY`
+- **Preferred object choice rationale:** this view already exposes bill identifiers, bill date, consumer identifiers, demand, arrears, and tariff/division fields in one place, so no additional join is required for a recent-bills query.
+### Row Grain
+- One row in `MV_BILLING_PAYMENT_HISTORY` represents one billing/payment-history row.
+- The same `CAN` can appear across multiple billing cycles, so both raw row count and distinct CAN count can be useful depending on the prompt.
+### Important Keys and Business Columns
+- **Consumer account identifier:** `CAN`
+- **Consumer id:** `CONSUMERID`
+- **Consumer name fields:** `FIRSTNAME`, `MIDDLENAME`, `LASTNAME`
+- **Bill identifier:** `BILLNO`
+- **Bill date:** `BILLDATE`
+- **Net amount:** `NETAMOUNT`
+- **Current month demand:** `CURRENTMONTHDEMAND`
+- **Arrear:** `ARREAR`
+- **Arrears interest:** `ARRINT`
+- **Division/section name:** `SECTION_ORG_NAME`
+- **Tariff description:** `TARIFF_DESCRIPTION`
+### Relationships
+- No extra join is required because the billing/history view already contains both the bill header detail and consumer-identifying fields needed for the output.
+### Lookup / Code Mappings
+- No separate lookup table is needed for this question.
+- Tariff and division fields are already available in readable business form in the billing view.
+### Date Semantics
+- For **?last 7 days?** in this run, use a rolling window based on the current date `2026-05-20`:
+  - `&gt;= TIMESTAMP '2026-05-13 00:00:00'`
+  - `&lt; TIMESTAMP '2026-05-21 00:00:00'`
+- Use `BILLDATE` as the bill-generation date.
+- The accessible billing snapshot spans `2025-01-01` through `2025-06-30`, so the requested window has no overlap with the available data.
+### Normalization Rules
+- Preserve raw bill rows when the user says ?display bills?.
+- Use `COUNT(DISTINCT CAN)` only as supporting context, not as the primary output, because the business entity requested is the bill row itself.
+- If the time window has no rows, return an explicit no-data result instead of an empty detail table.
+### Aggregation Rules
+- Safe pattern for this prompt:
+  - filter `MV_BILLING_PAYMENT_HISTORY` on `BILLDATE` for the rolling 7-day window
+  - compute row count and distinct CAN count for context
+  - return a capped detailed bill list ordered by `BILLDATE` descending when rows exist
+### Data Quality Notes
+- Because the requested 7-day window is entirely after the latest available billing date, the result is empty in this environment.
+- This is a source-coverage limitation, not evidence that the billing process generated no bills in the real system after June 2025.
+### Prompt-to-SQL Pattern
+- Typical user phrasing:
+  - ?Display bills generated in the last 7 days.?
+  - ?show recent bills from the last week?
+  - ?list bill rows created in the last 7 days?
+- Expected output type:
+  - detailed bill-row list when rows exist
+  - explicit no-data statement when the rolling window has no overlap with the snapshot
+### Output Contract
+- Return:
+  - Bill row count in window
+  - Distinct billed CANs in window
+  - Window start / end
+  - Detailed bill rows only if any exist
+### Confidence / Evidence
+- Source confidence: **high**
+- Reason: the billing view directly contains the date and bill detail needed, and the no-data outcome is fully explained by the snapshot date range.</t>
         </is>
       </c>
       <c r="G118" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>## SQL Details
+**Discovery Queries**
+```sql
+select min(billdate) as min_billdate,
+       max(billdate) as max_billdate,
+       count(*) as total_rows
+from mv_billing_payment_history;
+```
+**Lookup / Relationship Queries**
+```sql
+select count(*) as bill_rows_last_7_days,
+       count(distinct can) as distinct_cans_last_7_days,
+       min(billdate) as min_billdate_in_window,
+       max(billdate) as max_billdate_in_window
+from mv_billing_payment_history
+where billdate &gt;= timestamp '2026-05-13 00:00:00'
+  and billdate &lt; timestamp '2026-05-21 00:00:00';
+```
+**Final Business Queries**
+```sql
+select *
+from (
+  select can,
+         consumerid,
+         firstname,
+         middlename,
+         lastname,
+         billno,
+         billdate,
+         netamount,
+         currentmonthdemand,
+         arrear,
+         arrint,
+         section_org_name,
+         tariff_description
+  from mv_billing_payment_history
+  where billdate &gt;= timestamp '2026-05-13 00:00:00'
+    and billdate &lt; timestamp '2026-05-21 00:00:00'
+  order by billdate desc, billno desc
+)
+where rownum &lt;= 100;
+```</t>
         </is>
       </c>
       <c r="H118" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>10:27:58.417 - 10:28:34.220 (35.80s)
+Step breakdown:
+- Bill Date Range: `1.76s` total
+  - connect: `0.05s`
+  - execute: `1.70s`
+  - fetch: `0.00s`
+- Bills Last 7 Days: `0.09s` total
+  - connect: `0.06s`
+  - execute: `0.03s`
+  - fetch: `0.00s`
+- Bills Detail Last 7 Days: `0.08s` total
+  - connect: `0.06s`
+  - execute: `0.02s`
+  - fetch: `0.00s`</t>
         </is>
       </c>
       <c r="I118" s="22" t="inlineStr">
@@ -14684,32 +14805,194 @@
       </c>
       <c r="D119" s="21" t="inlineStr">
         <is>
+          <t>## Result
+Based on the available data, **all known sections in the accessible billing snapshot** qualify as having **no bills generated in the last month**.
+Supporting figures:
+| Metric | Value |
+|---|---:|
+| Distinct known sections in billing snapshot | 206 |
+| Bill rows in the last month | 0 |
+| Distinct sections billed in the last month | 0 |
+| Sections with no bills in the last month | 206 |
+| Requested window start | 2026-04-20 |
+| Requested window end | 2026-05-20 |
+This happens because the billing source `MV_BILLING_PAYMENT_HISTORY` currently contains data only from `2025-01-01` to `2025-06-30`, so there are no bill rows at all in the requested last-month window relative to the current system date.
+Sample section names from the known section universe:
+`99 Section (New,Unassigned)`, `ADARSHNAGAR`, `ADIBATLA (PD 1)`, `ADIKMET`, `AHMED NAGAR`, `ALIABAD`, `ALKAPURI`, `ALLABANDA`, `ALWAL`, `ALWAL (Div13)`, `AMBERPET`, `AMEENPUR (PD 8)`, `ASIF NAGAR`, `ASMANGARH`, `ATTAPUR`, `AUTONAGAR`.</t>
+        </is>
+      </c>
+      <c r="E119" s="22" t="inlineStr">
+        <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="E119" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
       <c r="F119" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>## Context Needed for Quicker Response
+### Canonical Objects
+- **Primary billing object:** `CTLHMWSSBTMP.MV_BILLING_PAYMENT_HISTORY`
+- **Candidate section-master object explored:** `CTLHMWSSBTMP.MDM_SWC_SECTION`
+- **Preferred object choice rationale:** `MV_BILLING_PAYMENT_HISTORY` exposes `SECTION_ORG_NAME`, `SECTION_ORG_CODE`, and `BILLDATE` directly. `MDM_SWC_SECTION` only exposed `CODE` and `DESCRIPTION`, and its alignment to the billing section universe was not validated strongly enough to replace the billing-derived section set in this run.
+### Row Grain
+- One row in `MV_BILLING_PAYMENT_HISTORY` represents one billing/payment-history row.
+- Multiple bill rows can exist for the same section, so section-level answers should use distinct section identifiers rather than raw row counts.
+### Important Keys and Business Columns
+- **Section code in billing source:** `SECTION_ORG_CODE`
+- **Section name in billing source:** `SECTION_ORG_NAME`
+- **Alternate section field in billing source:** `SECTIONCODE`
+- **Bill date:** `BILLDATE`
+- **Consumer account identifier:** `CAN`
+### Relationships
+- No join was required for the actual answer because the section universe and billed-section activity were both derived from `MV_BILLING_PAYMENT_HISTORY`.
+- If a future variant requires a true enterprise section master, validate `MV_BILLING_PAYMENT_HISTORY.SECTION_ORG_CODE -&gt; MDM_SWC_SECTION.CODE` before using it as the denominator.
+### Lookup / Code Mappings
+- No separate lookup table was required for this run.
+- Section names were used directly from `SECTION_ORG_NAME`.
+### Date Semantics
+- For **?last month?** in this run, use a rolling one-month window based on the current date `2026-05-20`:
+  - `&gt;= TIMESTAMP '2026-04-20 00:00:00'`
+  - `&lt; TIMESTAMP '2026-05-21 00:00:00'`
+- Use `BILLDATE` as the bill-generation date.
+- The accessible billing snapshot spans `2025-01-01` through `2025-06-30`, so the requested window has no overlap with the available data.
+### Normalization Rules
+- Use `SECTION_ORG_NAME` as the displayed section identity.
+- Use `COUNT(DISTINCT SECTION_ORG_NAME)` or `COUNT(DISTINCT SECTION_ORG_CODE)` when measuring the known section universe.
+- If no rows exist in the requested time window, treat every known section in the chosen denominator set as ?no bills generated.?
+### Aggregation Rules
+- Safe pattern for this question:
+  - derive the known section universe from the canonical section field in the billing source
+  - count billed sections in the requested rolling window
+  - derive no-bill sections as the remainder when the window has overlap
+  - if the window has zero bill rows, conclude that the full known section universe qualifies
+- If a full section list is needed, return the distinct section names from the denominator set.
+### Data Quality Notes
+- `MV_BILLING_PAYMENT_HISTORY` contains `206` distinct section names and `206` distinct section-org codes in the accessible snapshot.
+- The alternate `SECTIONCODE` field is not one-to-one with `SECTION_ORG_NAME`, so it should not be used alone as the display identity.
+- Because the requested last-month window is entirely after the latest available billing date, this is a source-coverage limitation rather than a live operational no-billing event.
+### Prompt-to-SQL Pattern
+- Typical user phrasing:
+  - ?Display sections where no bills were generated in the last month.?
+  - ?show sections with zero bill generation in the recent month?
+  - ?which sections had no bills in the last month?
+- Expected output type:
+  - section-level list or count summary
+  - explicit no-data-overlap explanation when the rolling window is outside the snapshot
+### Output Contract
+- Return:
+  - Distinct known sections in denominator
+  - Distinct billed sections in window
+  - Sections with no bills in window
+  - Window start / end
+  - Sample or full section names if requested
+### Confidence / Evidence
+- Source confidence: **medium-high**
+- Reason: the billing view directly exposes the section fields and the window has zero overlap, but the denominator was derived from the billing snapshot rather than a separately validated section master.</t>
         </is>
       </c>
       <c r="G119" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>## SQL Details
+**Discovery Queries**
+```sql
+select table_name, column_name
+from all_tab_columns
+where owner = USER
+  and (
+    upper(column_name) like '%SECTION%'
+    or upper(column_name) like '%ORG_NAME%'
+  )
+  and table_name in (
+    'MV_BILLING_PAYMENT_HISTORY',
+    'CONSUMER_CONNECTION_VIEW',
+    'MDM_SWC_SECTION',
+    'MDM_SWC_AREA'
+  )
+order by table_name, column_id;
+```
+```sql
+select column_id, column_name, data_type
+from user_tab_columns
+where table_name = 'MDM_SWC_SECTION'
+order by column_id;
+```
+```sql
+select min(billdate) as min_billdate,
+       max(billdate) as max_billdate,
+       count(*) as total_rows
+from mv_billing_payment_history;
+```
+**Lookup / Relationship Queries**
+```sql
+select count(distinct section_org_name) as distinct_section_names,
+       count(distinct section_org_code) as distinct_section_codes,
+       min(billdate) as min_billdate,
+       max(billdate) as max_billdate
+from mv_billing_payment_history;
+```
+```sql
+select count(*) as bill_rows_last_month,
+       count(distinct section_org_name) as billed_sections_last_month,
+       min(billdate) as min_billdate_in_window,
+       max(billdate) as max_billdate_in_window
+from mv_billing_payment_history
+where billdate &gt;= timestamp '2026-04-20 00:00:00'
+  and billdate &lt; timestamp '2026-05-21 00:00:00';
+```
+**Final Business Queries**
+```sql
+select *
+from (
+  select distinct section_org_code,
+         section_org_name,
+         sectioncode
+  from mv_billing_payment_history
+  where section_org_name is not null
+  order by section_org_name
+)
+where rownum &lt;= 30;
+```</t>
         </is>
       </c>
       <c r="H119" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>10:31:20.201 - 10:34:01.964 (161.76s)
+Step breakdown:
+- Section Source Discovery: `0.44s` total
+  - connect: `0.13s`
+  - execute: `0.30s`
+  - fetch: `0.00s`
+- Bill Date Range: `1.79s` total
+  - connect: `0.07s`
+  - execute: `1.71s`
+  - fetch: `0.00s`
+- Section Schema: `0.24s` total
+  - connect: `0.06s`
+  - execute: `0.18s`
+  - fetch: `0.00s`
+- Billing Sections: `55.09s` total
+  - connect: `0.08s`
+  - execute: `55.02s`
+  - fetch: `0.00s`
+- Section Samples From Billing: `54.61s` total
+  - connect: `0.28s`
+  - execute: `54.33s`
+  - fetch: `0.00s`
+- Sections Last Month: `0.08s` total
+  - connect: `0.07s`
+  - execute: `0.01s`
+  - fetch: `0.00s`</t>
         </is>
       </c>
       <c r="I119" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>Special attention needed: total runtime exceeded `45s`.
+Primary reason:
+- The delay was dominated by two expensive full-view section-discovery queries on `MV_BILLING_PAYMENT_HISTORY`.
+- `COUNT(DISTINCT SECTION_ORG_NAME / SECTION_ORG_CODE)` across the full billing view took about `55s`.
+- The distinct section sample query with ordering also took about `55s`.
+Optimization note:
+- For future section-level prompts, cache the known section universe once, or use a validated section master table if available.
+- Avoid repeated full-view `DISTINCT` + `ORDER BY` scans on `MV_BILLING_PAYMENT_HISTORY`.</t>
         </is>
       </c>
       <c r="J119" s="23" t="n"/>
@@ -14726,13 +15009,129 @@
           <t>Show the number of bills generated per day during January 2024.</t>
         </is>
       </c>
-      <c r="D120" s="5" t="n"/>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>## Result
+No bills were generated in **January 2024** in the available billing data, so there is no day-wise bill-count series to display for that month.
+Supporting figures:
+| Metric | Value |
+|---|---:|
+| Bill rows in January 2024 | 0 |
+| Distinct CANs billed in January 2024 | 0 |
+| Requested window start | 2024-01-01 |
+| Requested window end | 2024-01-31 |
+This happens because the billing source `MV_BILLING_PAYMENT_HISTORY` currently contains data only from `2025-01-01` to `2025-06-30`, so there are no bill rows at all for January 2024 in this environment.</t>
+        </is>
+      </c>
       <c r="E120" s="3" t="n"/>
-      <c r="F120" s="5" t="n"/>
-      <c r="G120" s="5" t="n"/>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>## Context Needed for Quicker Response
+### Canonical Objects
+- **Primary billing object:** `CTLHMWSSBTMP.MV_BILLING_PAYMENT_HISTORY`
+- **Preferred object choice rationale:** this view already exposes `BILLDATE`, `CAN`, and bill-level detail in one place, making it the natural source for day-wise bill-generation counts.
+### Row Grain
+- One row in `MV_BILLING_PAYMENT_HISTORY` represents one billing/payment-history row.
+- The same `CAN` can appear on different bill dates, so day-wise analysis should aggregate by date rather than consumer.
+### Important Keys and Business Columns
+- **Bill date:** `BILLDATE`
+- **Consumer account identifier:** `CAN`
+- **Bill identifier:** `BILLNO`
+- **Net amount:** `NETAMOUNT`
+### Relationships
+- No join is required for this question.
+- The day-wise count can be derived directly from the billing view by grouping on `TRUNC(BILLDATE)`.
+### Lookup / Code Mappings
+- No separate lookup table is needed.
+- Dates are taken directly from `BILLDATE` without any code mapping.
+### Date Semantics
+- For **?during January 2024?**, use a month-level half-open filter:
+  - `&gt;= TIMESTAMP '2024-01-01 00:00:00'`
+  - `&lt; TIMESTAMP '2024-02-01 00:00:00'`
+- Use `BILLDATE` as the bill-generation date.
+- The accessible billing snapshot spans `2025-01-01` through `2025-06-30`, so this requested month has no overlap with the available data.
+### Normalization Rules
+- Aggregate day-wise using `TRUNC(BILLDATE)`.
+- Use `COUNT(*)` as the bill-row metric.
+- Optionally include `COUNT(DISTINCT CAN)` as supporting context when needed.
+### Aggregation Rules
+- Safe pattern for this prompt:
+  - filter `MV_BILLING_PAYMENT_HISTORY` to January 2024
+  - group by `TRUNC(BILLDATE)`
+  - compute `COUNT(*)` as bill rows per day
+  - optionally compute `COUNT(DISTINCT CAN)` as distinct billed consumers per day
+- If the month has no rows, return an explicit no-data result instead of an empty chart/table.
+### Data Quality Notes
+- January 2024 is outside the accessible billing snapshot in this environment.
+- Therefore the day-wise series is empty because of source coverage, not because the business necessarily generated zero bills in the real system that month.
+### Prompt-to-SQL Pattern
+- Typical user phrasing:
+  - ?Show the number of bills generated per day during January 2024.?
+  - ?day-wise bill count for January 2024?
+  - ?daily bill generation trend for a month?
+- Expected output type:
+  - day-wise time series when rows exist
+  - explicit no-data statement when the requested month is missing from the snapshot
+### Output Contract
+- Return:
+  - Bill rows in month
+  - Distinct CANs in month
+  - Requested window start / end
+  - Day-wise bill counts only if rows exist
+### Confidence / Evidence
+- Source confidence: **high**
+- Reason: the billing view directly contains the date field needed for the aggregation, and the no-data result is fully explained by the snapshot coverage.</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>## SQL Details
+**Discovery Queries**
+```sql
+select min(billdate) as min_billdate,
+       max(billdate) as max_billdate,
+       count(*) as total_rows
+from mv_billing_payment_history;
+```
+**Lookup / Relationship Queries**
+```sql
+select count(*) as bill_rows_jan_2024,
+       count(distinct can) as distinct_cans_jan_2024,
+       min(billdate) as min_billdate_in_window,
+       max(billdate) as max_billdate_in_window
+from mv_billing_payment_history
+where billdate &gt;= timestamp '2024-01-01 00:00:00'
+  and billdate &lt; timestamp '2024-02-01 00:00:00';
+```
+**Final Business Queries**
+```sql
+select trunc(billdate) as bill_day,
+       count(*) as bill_rows,
+       count(distinct can) as distinct_cans
+from mv_billing_payment_history
+where billdate &gt;= timestamp '2024-01-01 00:00:00'
+  and billdate &lt; timestamp '2024-02-01 00:00:00'
+group by trunc(billdate)
+order by bill_day;
+```</t>
+        </is>
+      </c>
       <c r="H120" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>10:33:38.636 - 10:34:01.964 (23.33s)
+Step breakdown:
+- Bill Date Range Jan24: `1.74s` total
+  - connect: `0.09s`
+  - execute: `1.65s`
+  - fetch: `0.00s`
+- January 2024 Bill Coverage: `0.09s` total
+  - connect: `0.07s`
+  - execute: `0.02s`
+  - fetch: `0.00s`
+- Bills Per Day Jan24: `0.10s` total
+  - connect: `0.05s`
+  - execute: `0.05s`
+  - fetch: `0.00s`</t>
         </is>
       </c>
       <c r="I120" s="22" t="inlineStr">
@@ -14753,13 +15152,138 @@
           <t>Display the total demand generated for each tariff category in 2023.</t>
         </is>
       </c>
-      <c r="D121" s="5" t="n"/>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>## Result
+For **2023**, the accessible billing source returns **no total demand generated** for any tariff category.
+| Tariff Category | Tariff Description | Bill Rows | Billed CANs | Total Demand Generated |
+|---|---|---:|---:|---:|
+| 2023 total | No data | 0 | 0 | 0 |
+## Evidence
+- `MIN(BILLDATE)` = `2025-01-01`
+- `MAX(BILLDATE)` = `2025-06-30`
+- 2023 bill rows = `0`
+- 2023 billed CANs = `0`
+- 2023 total demand generated = `0`
+## Important Limitation
+This is a **no-data result due to source coverage**, not a business finding that no tariff-category demand existed in 2023.
+## Note
+For this prompt, **demand generated** was interpreted using `CURRENTMONTHDEMAND`, because that is the direct demand field exposed in `MV_BILLING_PAYMENT_HISTORY`.</t>
+        </is>
+      </c>
       <c r="E121" s="3" t="n"/>
-      <c r="F121" s="5" t="n"/>
-      <c r="G121" s="5" t="n"/>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>## Context Needed for Quicker Response
+### Canonical Objects
+- **Primary billing object:** `CTLHMWSSBTMP.MV_BILLING_PAYMENT_HISTORY`
+- **Preferred object choice rationale:** this view exposes `BILLDATE`, `TARIFFCATEGORY`, `TARIFF_DESCRIPTION`, `CURRENTMONTHDEMAND`, `NETAMOUNT`, and `CAN` in one place, so tariff-wise demand aggregation can be done without any join.
+### Row Grain
+- One row in `MV_BILLING_PAYMENT_HISTORY` represents one billing/payment-history row.
+- The same tariff category appears across many bill rows, so tariff summaries should aggregate over all matching bill rows.
+### Important Keys and Business Columns
+- **Tariff category code:** `TARIFFCATEGORY`
+- **Tariff description:** `TARIFF_DESCRIPTION`
+- **Bill date:** `BILLDATE`
+- **Demand field used for this prompt:** `CURRENTMONTHDEMAND`
+- **Alternative billed-amount field present in the same source:** `NETAMOUNT`
+- **Consumer account identifier:** `CAN`
+### Relationships
+- No extra join is required because the billing/history view already contains both the tariff fields and the demand field needed for the answer.
+### Lookup / Code Mappings
+- `TARIFF_DESCRIPTION` is already available alongside `TARIFFCATEGORY`, so no separate tariff lookup is required.
+- `CURRENTMONTHDEMAND` is the direct demand-style field; `NETAMOUNT` is better treated as billed/payable amount, not raw demand.
+### Date Semantics
+- For **?in 2023?**, use a full-year half-open filter on `BILLDATE`:
+  - `&gt;= TIMESTAMP '2023-01-01 00:00:00'`
+  - `&lt; TIMESTAMP '2024-01-01 00:00:00'`
+- The accessible billing snapshot spans `2025-01-01` through `2025-06-30`, so 2023 has no overlap with the available data.
+### Normalization Rules
+- Group by both `TARIFFCATEGORY` and `TARIFF_DESCRIPTION`.
+- Use `NVL(..., 'UNKNOWN')` if null tariff values need to be surfaced explicitly.
+- Keep billed-CAN count as supporting context, but sum demand over bill rows.
+### Aggregation Rules
+- Interpret **?total demand generated?** as `SUM(CURRENTMONTHDEMAND)`.
+- Safe pattern for this question:
+  - filter by `BILLDATE` for calendar year 2023
+  - group by tariff category and tariff description
+  - compute `COUNT(*)` as bill rows
+  - compute `COUNT(DISTINCT CAN)` as billed CANs
+  - compute `SUM(CURRENTMONTHDEMAND)` as total demand generated
+### Data Quality Notes
+- The accessible billing snapshot contains no 2023 rows.
+- Therefore the tariff-wise demand result is empty because of source coverage, not because the tariff categories necessarily had zero demand in the live business period.
+### Prompt-to-SQL Pattern
+- Typical user phrasing:
+  - ?Display the total demand generated for each tariff category in 2023.?
+  - ?tariff-wise total demand for 2023?
+  - ?sum demand by tariff category for a year?
+- Expected output type:
+  - tariff-wise grouped summary when the year exists
+  - explicit no-data statement when the year is outside the accessible snapshot
+### Output Contract
+- Return:
+  - Tariff Category
+  - Tariff Description
+  - Bill Rows
+  - Billed CANs
+  - Total Demand Generated
+### Confidence / Evidence
+- Source confidence: **high**
+- Reason: the billing view directly exposes the tariff and demand fields needed, and the no-data outcome is fully explained by the snapshot date range.</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>## SQL Details
+**Discovery Queries**
+```sql
+select column_name
+from user_tab_columns
+where table_name = 'MV_BILLING_PAYMENT_HISTORY'
+  and (
+    upper(column_name) like '%TARIFF%'
+    or upper(column_name) like '%DEMAND%'
+    or upper(column_name) like '%NETAMOUNT%'
+    or upper(column_name) like '%BILLDATE%'
+  )
+order by column_name;
+```
+```sql
+select min(billdate) as min_billdate,
+       max(billdate) as max_billdate,
+       count(*) as total_rows
+from mv_billing_payment_history;
+```
+**Lookup / Relationship Queries**
+```sql
+select count(*) as bill_rows_2023,
+       count(distinct can) as billed_cans_2023,
+       sum(currentmonthdemand) as total_current_month_demand_2023,
+       min(billdate) as min_billdate_in_window,
+       max(billdate) as max_billdate_in_window
+from mv_billing_payment_history
+where billdate &gt;= timestamp '2023-01-01 00:00:00'
+  and billdate &lt; timestamp '2024-01-01 00:00:00';
+```
+**Final Business Queries**
+```sql
+select nvl(tariffcategory, 'UNKNOWN') as tariff_category,
+       nvl(tariff_description, 'UNKNOWN') as tariff_description,
+       count(*) as bill_rows,
+       count(distinct can) as billed_cans,
+       sum(currentmonthdemand) as total_current_month_demand
+from mv_billing_payment_history
+where billdate &gt;= timestamp '2023-01-01 00:00:00'
+  and billdate &lt; timestamp '2024-01-01 00:00:00'
+group by nvl(tariffcategory, 'UNKNOWN'), nvl(tariff_description, 'UNKNOWN')
+order by total_current_month_demand desc nulls last, tariff_category;
+```</t>
+        </is>
+      </c>
       <c r="H121" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>10:45:34.855 - 10:46:06.000 (31.15s)</t>
         </is>
       </c>
       <c r="I121" s="22" t="inlineStr">
@@ -14780,13 +15304,114 @@
           <t>Show the number of consumers billed under each tariff category in 2023.</t>
         </is>
       </c>
-      <c r="D122" s="5" t="n"/>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>## Result
+For **2023**, the accessible billing source returns **no billed consumers** under any tariff category.
+| Tariff Category | Tariff Description | Number of Consumers Billed | Bill Rows |
+|---|---|---:|---:|
+| 2023 total | No data | 0 | 0 |
+## Evidence
+- `MIN(BILLDATE)` = `2025-01-01`
+- `MAX(BILLDATE)` = `2025-06-30`
+- 2023 bill rows = `0`
+- 2023 billed CANs = `0`
+## Important Limitation
+This is a **no-data result due to source coverage**, not a business finding that no consumers were billed in 2023.</t>
+        </is>
+      </c>
       <c r="E122" s="3" t="n"/>
-      <c r="F122" s="5" t="n"/>
-      <c r="G122" s="5" t="n"/>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>## Context Needed for Quicker Response
+### Canonical Objects
+- **Primary billing object:** `CTLHMWSSBTMP.MV_BILLING_PAYMENT_HISTORY`
+- **Preferred object choice rationale:** this view exposes `BILLDATE`, `TARIFFCATEGORY`, `TARIFF_DESCRIPTION`, and `CAN` in one place, so tariff-wise billed-consumer counts can be computed without any join.
+### Row Grain
+- One row in `MV_BILLING_PAYMENT_HISTORY` represents one billing/payment-history row.
+- The same consumer (`CAN`) can appear multiple times, so billed-consumer counts must use `COUNT(DISTINCT CAN)` rather than raw bill-row counts.
+### Important Keys and Business Columns
+- **Tariff category code:** `TARIFFCATEGORY`
+- **Tariff description:** `TARIFF_DESCRIPTION`
+- **Consumer account identifier:** `CAN`
+- **Bill date:** `BILLDATE`
+- **Bill identifier:** `BILLNO`
+### Relationships
+- No extra join is required because the billing/history view already contains both the tariff fields and the consumer identifier needed for the answer.
+### Lookup / Code Mappings
+- `TARIFF_DESCRIPTION` is already available alongside `TARIFFCATEGORY`, so no separate tariff lookup is required.
+- `CAN` is the stable billed-consumer key for this question family.
+### Date Semantics
+- For **?in 2023?**, use a full-year half-open filter on `BILLDATE`:
+  - `&gt;= TIMESTAMP '2023-01-01 00:00:00'`
+  - `&lt; TIMESTAMP '2024-01-01 00:00:00'`
+- The accessible billing snapshot spans `2025-01-01` through `2025-06-30`, so 2023 has no overlap with the available data.
+### Normalization Rules
+- Group by both `TARIFFCATEGORY` and `TARIFF_DESCRIPTION`.
+- Use `COUNT(DISTINCT CAN)` as the primary billed-consumer metric.
+- Keep raw `COUNT(*)` bill rows as supporting context when useful.
+### Aggregation Rules
+- Interpret **?number of consumers billed?** as `COUNT(DISTINCT CAN)`.
+- Safe pattern for this question:
+  - filter by `BILLDATE` for calendar year 2023
+  - group by tariff category and tariff description
+  - compute `COUNT(DISTINCT CAN)` as billed consumers
+  - optionally compute `COUNT(*)` as bill rows
+### Data Quality Notes
+- The accessible billing snapshot contains no 2023 rows.
+- Therefore the tariff-wise billed-consumer result is empty because of source coverage, not because tariff categories necessarily had zero billed consumers in the live business period.
+### Prompt-to-SQL Pattern
+- Typical user phrasing:
+  - ?Show the number of consumers billed under each tariff category in 2023.?
+  - ?tariff-wise billed consumer count for 2023?
+  - ?how many consumers were billed by tariff category in a year?
+- Expected output type:
+  - tariff-wise grouped summary when the year exists
+  - explicit no-data statement when the year is outside the accessible snapshot
+### Output Contract
+- Return:
+  - Tariff Category
+  - Tariff Description
+  - Number of Consumers Billed
+  - Bill Rows
+### Confidence / Evidence
+- Source confidence: **high**
+- Reason: the billing view directly exposes the tariff and consumer fields needed, and the no-data outcome is fully explained by the snapshot date range.</t>
+        </is>
+      </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>## SQL Details
+**Discovery Queries**
+None used for this question.
+Reason: the canonical billing/history source and the tariff / consumer fields had already been established in the immediately preceding closely related tariff-demand run.
+**Lookup / Relationship Queries**
+```sql
+select count(*) as bill_rows_2023,
+       count(distinct can) as billed_cans_2023,
+       min(billdate) as min_billdate_in_window,
+       max(billdate) as max_billdate_in_window
+from mv_billing_payment_history
+where billdate &gt;= timestamp '2023-01-01 00:00:00'
+  and billdate &lt; timestamp '2024-01-01 00:00:00';
+```
+**Final Business Queries**
+```sql
+select nvl(tariffcategory, 'UNKNOWN') as tariff_category,
+       nvl(tariff_description, 'UNKNOWN') as tariff_description,
+       count(distinct can) as billed_cans,
+       count(*) as bill_rows
+from mv_billing_payment_history
+where billdate &gt;= timestamp '2023-01-01 00:00:00'
+  and billdate &lt; timestamp '2024-01-01 00:00:00'
+group by nvl(tariffcategory, 'UNKNOWN'), nvl(tariff_description, 'UNKNOWN')
+order by billed_cans desc, tariff_category;
+```</t>
+        </is>
+      </c>
       <c r="H122" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>10:46:24.592 - 10:46:49.000 (24.41s)</t>
         </is>
       </c>
       <c r="I122" s="22" t="inlineStr">
@@ -14807,18 +15432,148 @@
           <t>Show the average demand per bill for each tariff category.</t>
         </is>
       </c>
-      <c r="D123" s="5" t="n"/>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>## Result
+Here is the **average demand per bill for each tariff category** from the accessible billing snapshot.
+| Tariff Category | Tariff Description | Bill Rows | Billed CANs | Average Demand per Bill | Total Demand |
+|---|---|---:|---:|---:|---:|
+| V | GRAM PANCHAYAT | 121 | 8 | 4,697,154.81 | 568,355,732.00 |
+| X | MIX CATEGORY | 109 | 14 | 3,289,932.06 | 358,602,594.89 |
+| CB | CANTONMENT BOARD | 120 | 17 | 2,413,668.00 | 289,640,160.00 |
+| XO | MIX CATEGORY OTHERS | 8 | 1 | 1,744,410.88 | 13,955,287.00 |
+| BC | BULK COMMERCIAL | 771 | 75 | 979,534.74 | 755,221,284.96 |
+| IW | INDUSTRY(WATBAS | 807 | 72 | 953,946.77 | 769,835,041.96 |
+| S | SURR.MUNICIP | 36 | 2 | 752,235.00 | 27,080,460.00 |
+| I1 | INDUSTRIES-BULK | 5,363 | 547 | 672,530.47 | 3,606,780,896.51 |
+| O | COLONIES | 11,109 | 1,025 | 87,292.12 | 969,728,175.51 |
+| D | DOMESTIC | 11,602,644 | 904,176 | 69,690.63 | 808,595,583,631.15 |
+| C | COMMERCIAL | 664,509 | 57,415 | 23,687.54 | 15,740,582,697.75 |
+| M3 | MASC-NONDOMESTI | 48,257 | 4,791 | 12,879.79 | 621,539,793.00 |
+| RC | RELIG.CHAR.INST | 2,788 | 350 | 4,486.71 | 12,508,946.25 |
+| I | INDUSTRIES | 17,105 | 1,482 | 4,181.37 | 71,522,386.43 |
+| M4 | MSB-INDIVIDUAL | 7,525 | 794 | 3,633.02 | 27,338,450.55 |
+| M1 | MSAC-DOMESTIC | 371,036 | 36,550 | 3,229.62 | 1,198,306,301.95 |
+| M2 | MASC-MIXED | 10,334 | 984 | 3,221.71 | 33,293,151.45 |
+| M0 | DOMESTIC WITH FLATS | 154,800 | 13,907 | 2,362.96 | 365,785,845.83 |
+| N | CONSTRUCTION | 30,914 | 2,913 | 1,900.62 | 58,755,832.10 |
+| CH | SUPPLY TO CHARITY INSTITUTIONS | 463 | 58 | 1,552.59 | 718,847.50 |
+| MB | MULTISTORIED BUILDINGS | 19 | 3 | 1,174.34 | 22,312.50 |
+| DM | DOMESTIC-MUN | 1,486,529 | 119,450 | 817.10 | 1,214,640,854.75 |
+| DS | DOMESTIC-SLUMS | 3,670,321 | 245,073 | 169.13 | 620,770,256.95 |
+| FS | FILLING STATION | 228 | 65 | 0.00 | 0.00 |
+| PS | PUBLICSTANDPOST | 4,440 | 709 | 0.00 | 0.00 |
+Overall snapshot average demand per bill: **46,208.08**.
+## Note
+For this prompt, **demand per bill** was interpreted using `CURRENTMONTHDEMAND`, because that is the direct demand field exposed in `MV_BILLING_PAYMENT_HISTORY`.</t>
+        </is>
+      </c>
       <c r="E123" s="3" t="n"/>
-      <c r="F123" s="5" t="n"/>
-      <c r="G123" s="5" t="n"/>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>## Context Needed for Quicker Response
+### Canonical Objects
+- **Primary billing object:** `CTLHMWSSBTMP.MV_BILLING_PAYMENT_HISTORY`
+- **Preferred object choice rationale:** this view exposes `TARIFFCATEGORY`, `TARIFF_DESCRIPTION`, `CURRENTMONTHDEMAND`, `BILLDATE`, `CAN`, and `BILLNO` in one place, so tariff-wise demand averages can be computed without any join.
+### Row Grain
+- One row in `MV_BILLING_PAYMENT_HISTORY` represents one billing/payment-history row.
+- Average demand per bill should therefore be calculated over bill rows, not over consumers.
+### Important Keys and Business Columns
+- **Tariff category code:** `TARIFFCATEGORY`
+- **Tariff description:** `TARIFF_DESCRIPTION`
+- **Demand field used for this prompt:** `CURRENTMONTHDEMAND`
+- **Alternative billed-amount field present in same source:** `NETAMOUNT`
+- **Consumer account identifier:** `CAN`
+- **Bill identifier:** `BILLNO`
+- **Bill date:** `BILLDATE`
+### Relationships
+- No extra join is required because the billing/history view already contains both the tariff fields and the demand field needed for the answer.
+### Lookup / Code Mappings
+- `TARIFF_DESCRIPTION` is already available alongside `TARIFFCATEGORY`, so no separate tariff lookup is required.
+- `CURRENTMONTHDEMAND` is the direct demand-style field; `NETAMOUNT` should be treated as billed/payable amount, not raw demand.
+### Date Semantics
+- This prompt did not ask for a period filter.
+- Therefore the full accessible billing snapshot was used.
+- The current accessible snapshot spans `2025-01-01` through `2025-06-30`.
+### Normalization Rules
+- Group by both `TARIFFCATEGORY` and `TARIFF_DESCRIPTION`.
+- Use `AVG(CURRENTMONTHDEMAND)` for average demand per bill.
+- Keep `COUNT(*)` as bill-row context and `COUNT(DISTINCT CAN)` as billed-consumer context.
+### Aggregation Rules
+- Interpret **?average demand per bill?** as `AVG(CURRENTMONTHDEMAND)` over bill rows.
+- Safe pattern for this question:
+  - group by tariff category and tariff description
+  - compute `COUNT(*)` as bill rows
+  - compute `COUNT(DISTINCT CAN)` as billed CANs
+  - compute `AVG(CURRENTMONTHDEMAND)` as average demand per bill
+  - optionally compute `SUM(CURRENTMONTHDEMAND)` as supporting total demand
+### Data Quality Notes
+- Some tariff categories such as `FS` and `PS` currently show zero average demand because their total `CURRENTMONTHDEMAND` is zero in the accessible snapshot.
+- Rare tariff categories with very small row counts can dominate the ranking by average demand per bill, so bill-row counts should be shown alongside the averages.
+### Prompt-to-SQL Pattern
+- Typical user phrasing:
+  - ?Show the average demand per bill for each tariff category.?
+  - ?tariff-wise average demand per bill?
+  - ?average bill demand by tariff category?
+- Expected output type:
+  - tariff-wise grouped summary ranked by average demand per bill
+### Output Contract
+- Return:
+  - Tariff Category
+  - Tariff Description
+  - Bill Rows
+  - Billed CANs
+  - Average Demand per Bill
+  - optionally Total Demand
+### Confidence / Evidence
+- Source confidence: **high**
+- Reason: the billing view directly exposes the tariff and demand fields needed, and the aggregation grain matches the wording of the prompt.</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>## SQL Details
+**Discovery Queries**
+None used for this question.
+Reason: the canonical billing/history source and the tariff / demand fields had already been established in the immediately preceding closely related tariff-demand runs.
+**Lookup / Relationship Queries**
+```sql
+select count(*) as bill_rows,
+       count(distinct can) as billed_cans,
+       min(billdate) as min_billdate,
+       max(billdate) as max_billdate,
+       avg(currentmonthdemand) as avg_current_month_demand
+from mv_billing_payment_history;
+```
+**Final Business Queries**
+```sql
+select nvl(tariffcategory, 'UNKNOWN') as tariff_category,
+       nvl(tariff_description, 'UNKNOWN') as tariff_description,
+       count(*) as bill_rows,
+       count(distinct can) as billed_cans,
+       avg(currentmonthdemand) as avg_current_month_demand_per_bill,
+       sum(currentmonthdemand) as total_current_month_demand
+from mv_billing_payment_history
+group by nvl(tariffcategory, 'UNKNOWN'), nvl(tariff_description, 'UNKNOWN')
+order by avg_current_month_demand_per_bill desc nulls last, tariff_category;
+```</t>
+        </is>
+      </c>
       <c r="H123" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>10:47:10.233 - 10:48:23.887 (73.65s)</t>
         </is>
       </c>
       <c r="I123" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>Special attention needed: total runtime exceeded `45s`.
+Primary reason:
+- The runtime was dominated by two full-view aggregates on `MV_BILLING_PAYMENT_HISTORY`.
+- The overall coverage query with `AVG(CURRENTMONTHDEMAND)` and `COUNT(DISTINCT CAN)` took about `25.94s`.
+- The tariff-wise grouped average-demand query took about `32.25s`.
+Optimization note:
+- Avoid repeated whole-view average and distinct-count scans when similar tariff-demand metrics have already been computed in nearby prompts.
+- Caching tariff-wise aggregates for the active snapshot would significantly reduce runtime for this question family.</t>
         </is>
       </c>
     </row>
@@ -14836,12 +15591,132 @@
           <t>Show the average demand per bill for each tariff category in January 2023.</t>
         </is>
       </c>
-      <c r="D124" s="5" t="n"/>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>## Result
+For **January 2023**, the accessible billing source returns **no average demand per bill** for any tariff category.
+| Tariff Category | Tariff Description | Bill Rows | Billed CANs | Average Demand per Bill | Total Demand |
+|---|---|---:|---:|---:|---:|
+| 2023-01 total | No data | 0 | 0 | 0 | 0 |
+## Evidence
+- `MIN(BILLDATE)` = `2025-01-01`
+- `MAX(BILLDATE)` = `2025-06-30`
+- January 2023 bill rows = `0`
+- January 2023 billed CANs = `0`
+- January 2023 average demand per bill = `0`
+## Important Limitation
+This is a **no-data result due to source coverage**, not a business finding that tariff categories had zero bill demand in January 2023.
+## Note
+For this prompt, **demand per bill** was interpreted using `CURRENTMONTHDEMAND`, because that is the direct demand field exposed in `MV_BILLING_PAYMENT_HISTORY`.</t>
+        </is>
+      </c>
       <c r="E124" s="3" t="n"/>
-      <c r="F124" s="5" t="n"/>
-      <c r="G124" s="5" t="n"/>
-      <c r="H124" s="12" t="n"/>
-      <c r="I124" s="1" t="n"/>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>## Context Needed for Quicker Response
+### Canonical Objects
+- **Primary billing object:** `CTLHMWSSBTMP.MV_BILLING_PAYMENT_HISTORY`
+- **Preferred object choice rationale:** this view exposes `TARIFFCATEGORY`, `TARIFF_DESCRIPTION`, `CURRENTMONTHDEMAND`, `BILLDATE`, `CAN`, and `BILLNO` in one place, so tariff-wise demand averages for a month can be computed without any join.
+### Row Grain
+- One row in `MV_BILLING_PAYMENT_HISTORY` represents one billing/payment-history row.
+- Average demand per bill should therefore be calculated over bill rows, not over consumers.
+### Important Keys and Business Columns
+- **Tariff category code:** `TARIFFCATEGORY`
+- **Tariff description:** `TARIFF_DESCRIPTION`
+- **Demand field used for this prompt:** `CURRENTMONTHDEMAND`
+- **Consumer account identifier:** `CAN`
+- **Bill identifier:** `BILLNO`
+- **Bill date:** `BILLDATE`
+### Relationships
+- No extra join is required because the billing/history view already contains both the tariff fields and the demand field needed for the answer.
+### Lookup / Code Mappings
+- `TARIFF_DESCRIPTION` is already available alongside `TARIFFCATEGORY`, so no separate tariff lookup is required.
+- `CURRENTMONTHDEMAND` is the direct demand-style field.
+### Date Semantics
+- For **?in January 2023?**, use a month-level half-open filter on `BILLDATE`:
+  - `&gt;= TIMESTAMP '2023-01-01 00:00:00'`
+  - `&lt; TIMESTAMP '2023-02-01 00:00:00'`
+- The accessible billing snapshot spans `2025-01-01` through `2025-06-30`, so January 2023 has no overlap with the available data.
+### Normalization Rules
+- Group by both `TARIFFCATEGORY` and `TARIFF_DESCRIPTION`.
+- Use `AVG(CURRENTMONTHDEMAND)` for average demand per bill.
+- Keep `COUNT(*)` as bill-row context and `COUNT(DISTINCT CAN)` as billed-consumer context.
+### Aggregation Rules
+- Interpret **?average demand per bill?** as `AVG(CURRENTMONTHDEMAND)` over bill rows.
+- Safe pattern for this question:
+  - filter to January 2023 using `BILLDATE`
+  - group by tariff category and tariff description
+  - compute `COUNT(*)` as bill rows
+  - compute `COUNT(DISTINCT CAN)` as billed CANs
+  - compute `AVG(CURRENTMONTHDEMAND)` as average demand per bill
+  - optionally compute `SUM(CURRENTMONTHDEMAND)` as supporting total demand
+### Data Quality Notes
+- The accessible billing snapshot contains no January 2023 rows.
+- Therefore the tariff-wise average-demand result is empty because of source coverage, not because tariff categories necessarily had zero demand in the live business period.
+### Prompt-to-SQL Pattern
+- Typical user phrasing:
+  - ?Show the average demand per bill for each tariff category in January 2023.?
+  - ?tariff-wise average demand per bill for January 2023?
+  - ?average bill demand by tariff category in a month?
+- Expected output type:
+  - tariff-wise grouped summary when the month exists
+  - explicit no-data statement when the month is outside the accessible snapshot
+### Output Contract
+- Return:
+  - Tariff Category
+  - Tariff Description
+  - Bill Rows
+  - Billed CANs
+  - Average Demand per Bill
+  - optionally Total Demand
+### Confidence / Evidence
+- Source confidence: **high**
+- Reason: the billing view directly exposes the tariff and demand fields needed, and the no-data outcome is fully explained by the snapshot date range.</t>
+        </is>
+      </c>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>## SQL Details
+**Discovery Queries**
+None used for this question.
+Reason: the canonical billing/history source and the tariff / demand fields had already been established in the immediately preceding closely related tariff-demand runs.
+**Lookup / Relationship Queries**
+```sql
+select count(*) as bill_rows_jan_2023,
+       count(distinct can) as billed_cans_jan_2023,
+       avg(currentmonthdemand) as avg_current_month_demand_jan_2023,
+       min(billdate) as min_billdate_in_window,
+       max(billdate) as max_billdate_in_window
+from mv_billing_payment_history
+where billdate &gt;= timestamp '2023-01-01 00:00:00'
+  and billdate &lt; timestamp '2023-02-01 00:00:00';
+```
+**Final Business Queries**
+```sql
+select nvl(tariffcategory, 'UNKNOWN') as tariff_category,
+       nvl(tariff_description, 'UNKNOWN') as tariff_description,
+       count(*) as bill_rows,
+       count(distinct can) as billed_cans,
+       avg(currentmonthdemand) as avg_current_month_demand_per_bill,
+       sum(currentmonthdemand) as total_current_month_demand
+from mv_billing_payment_history
+where billdate &gt;= timestamp '2023-01-01 00:00:00'
+  and billdate &lt; timestamp '2023-02-01 00:00:00'
+group by nvl(tariffcategory, 'UNKNOWN'), nvl(tariff_description, 'UNKNOWN')
+order by avg_current_month_demand_per_bill desc nulls last, tariff_category;
+```</t>
+        </is>
+      </c>
+      <c r="H124" s="12" t="inlineStr">
+        <is>
+          <t>10:49:22.110 - 10:49:43.000 (20.89s)</t>
+        </is>
+      </c>
+      <c r="I124" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="30" customHeight="1">
       <c r="A125" s="3" t="n">
@@ -14855,12 +15730,130 @@
           <t>Show tariff categories where total demand exceeded 10000000 in 2023.</t>
         </is>
       </c>
-      <c r="D125" s="5" t="n"/>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>## Result
+For **2023**, the accessible billing source returns **no tariff categories** where total demand exceeded `10,000,000`.
+| Tariff Category | Tariff Description | Bill Rows | Billed CANs | Total Demand Generated |
+|---|---|---:|---:|---:|
+| 2023 total | No data | 0 | 0 | 0 |
+## Evidence
+- `MIN(BILLDATE)` = `2025-01-01`
+- `MAX(BILLDATE)` = `2025-06-30`
+- 2023 bill rows = `0`
+- 2023 billed CANs = `0`
+- 2023 total demand generated = `0`
+- 2023 tariff groups above `10,000,000` demand = `0`
+## Important Limitation
+This is a **no-data result due to source coverage**, not a business finding that no tariff category crossed the threshold in 2023.
+## Note
+For this prompt, **demand generated** was interpreted using `CURRENTMONTHDEMAND`, because that is the direct demand field exposed in `MV_BILLING_PAYMENT_HISTORY`.</t>
+        </is>
+      </c>
       <c r="E125" s="3" t="n"/>
-      <c r="F125" s="5" t="n"/>
-      <c r="G125" s="5" t="n"/>
-      <c r="H125" s="12" t="n"/>
-      <c r="I125" s="1" t="n"/>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>## Context Needed for Quicker Response
+### Canonical Objects
+- **Primary billing object:** `CTLHMWSSBTMP.MV_BILLING_PAYMENT_HISTORY`
+- **Preferred object choice rationale:** this view exposes `TARIFFCATEGORY`, `TARIFF_DESCRIPTION`, `CURRENTMONTHDEMAND`, `BILLDATE`, and `CAN` in one place, so tariff-wise threshold filtering can be done without any join.
+### Row Grain
+- One row in `MV_BILLING_PAYMENT_HISTORY` represents one billing/payment-history row.
+- Threshold checks must aggregate demand by tariff category across all matching bill rows in the requested period.
+### Important Keys and Business Columns
+- **Tariff category code:** `TARIFFCATEGORY`
+- **Tariff description:** `TARIFF_DESCRIPTION`
+- **Demand field used for this prompt:** `CURRENTMONTHDEMAND`
+- **Consumer account identifier:** `CAN`
+- **Bill date:** `BILLDATE`
+### Relationships
+- No extra join is required because the billing/history view already contains both the tariff fields and the demand field needed for the threshold check.
+### Lookup / Code Mappings
+- `TARIFF_DESCRIPTION` is already available alongside `TARIFFCATEGORY`, so no separate tariff lookup is required.
+- `CURRENTMONTHDEMAND` is the direct demand-style field.
+### Date Semantics
+- For **?in 2023?**, use a full-year half-open filter on `BILLDATE`:
+  - `&gt;= TIMESTAMP '2023-01-01 00:00:00'`
+  - `&lt; TIMESTAMP '2024-01-01 00:00:00'`
+- The accessible billing snapshot spans `2025-01-01` through `2025-06-30`, so 2023 has no overlap with the available data.
+### Normalization Rules
+- Group by both `TARIFFCATEGORY` and `TARIFF_DESCRIPTION`.
+- Use `SUM(CURRENTMONTHDEMAND)` as the tariff-level demand total.
+- Apply the threshold after aggregation using `HAVING`.
+### Aggregation Rules
+- Interpret **?total demand exceeded 10000000?** as `SUM(CURRENTMONTHDEMAND) &gt; 10000000`.
+- Safe pattern for this question:
+  - filter by `BILLDATE` for calendar year 2023
+  - group by tariff category and tariff description
+  - compute `SUM(CURRENTMONTHDEMAND)` as total demand generated
+  - filter grouped rows with `HAVING SUM(CURRENTMONTHDEMAND) &gt; 10000000`
+  - optionally include bill rows and billed CANs as supporting context
+### Data Quality Notes
+- The accessible billing snapshot contains no 2023 rows.
+- Therefore the threshold result is empty because of source coverage, not because tariff categories necessarily stayed below the threshold in the live business period.
+### Prompt-to-SQL Pattern
+- Typical user phrasing:
+  - ?Show tariff categories where total demand exceeded 10000000 in 2023.?
+  - ?tariff categories above a demand threshold for 2023?
+  - ?filter tariff-wise demand by threshold in a year?
+- Expected output type:
+  - threshold-filtered tariff summary when the year exists
+  - explicit no-data statement when the year is outside the accessible snapshot
+### Output Contract
+- Return:
+  - Tariff Category
+  - Tariff Description
+  - Bill Rows
+  - Billed CANs
+  - Total Demand Generated
+### Confidence / Evidence
+- Source confidence: **high**
+- Reason: the billing view directly exposes the tariff and demand fields needed, and the no-data outcome is fully explained by the snapshot date range.</t>
+        </is>
+      </c>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>## SQL Details
+**Discovery Queries**
+None used for this question.
+Reason: the canonical billing/history source and the tariff / demand fields had already been established in the immediately preceding closely related tariff-demand runs.
+**Lookup / Relationship Queries**
+```sql
+select count(*) as bill_rows_2023,
+       count(distinct can) as billed_cans_2023,
+       sum(currentmonthdemand) as total_current_month_demand_2023,
+       min(billdate) as min_billdate_in_window,
+       max(billdate) as max_billdate_in_window
+from mv_billing_payment_history
+where billdate &gt;= timestamp '2023-01-01 00:00:00'
+  and billdate &lt; timestamp '2024-01-01 00:00:00';
+```
+**Final Business Queries**
+```sql
+select nvl(tariffcategory, 'UNKNOWN') as tariff_category,
+       nvl(tariff_description, 'UNKNOWN') as tariff_description,
+       count(*) as bill_rows,
+       count(distinct can) as billed_cans,
+       sum(currentmonthdemand) as total_current_month_demand
+from mv_billing_payment_history
+where billdate &gt;= timestamp '2023-01-01 00:00:00'
+  and billdate &lt; timestamp '2024-01-01 00:00:00'
+group by nvl(tariffcategory, 'UNKNOWN'), nvl(tariff_description, 'UNKNOWN')
+having sum(currentmonthdemand) &gt; 10000000
+order by total_current_month_demand desc, tariff_category;
+```</t>
+        </is>
+      </c>
+      <c r="H125" s="12" t="inlineStr">
+        <is>
+          <t>10:50:12.146 - 10:50:35.000 (22.85s)</t>
+        </is>
+      </c>
+      <c r="I125" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="30" customHeight="1">
       <c r="A126" s="3" t="n">
@@ -14874,12 +15867,132 @@
           <t>Show the average bill amount per consumer in 2023.</t>
         </is>
       </c>
-      <c r="D126" s="5" t="n"/>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>## Result
+For **2023**, the accessible billing source returns **no average bill amount per consumer**.
+| Consumer Scope | Bill Rows | Billed CANs | Average Bill Amount |
+|---|---:|---:|---:|
+| 2023 total | 0 | 0 | 0 |
+## Evidence
+- `MIN(BILLDATE)` = `2025-01-01`
+- `MAX(BILLDATE)` = `2025-06-30`
+- 2023 bill rows = `0`
+- 2023 billed CANs = `0`
+- 2023 average bill amount = `0`
+## Important Limitation
+This is a **no-data result due to source coverage**, not a business finding that consumers had zero bill amount in 2023.
+## Note
+For this prompt, **bill amount** was interpreted using `NETAMOUNT`, because that is the billed/payable amount field exposed in `MV_BILLING_PAYMENT_HISTORY`.</t>
+        </is>
+      </c>
       <c r="E126" s="3" t="n"/>
-      <c r="F126" s="5" t="n"/>
-      <c r="G126" s="5" t="n"/>
-      <c r="H126" s="12" t="n"/>
-      <c r="I126" s="1" t="n"/>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>## Context Needed for Quicker Response
+### Canonical Objects
+- **Primary billing object:** `CTLHMWSSBTMP.MV_BILLING_PAYMENT_HISTORY`
+- **Preferred object choice rationale:** this view exposes `CAN`, consumer-name fields, `NETAMOUNT`, and `BILLDATE` in one place, so consumer-level average bill amount can be computed without any join.
+### Row Grain
+- One row in `MV_BILLING_PAYMENT_HISTORY` represents one billing/payment-history row.
+- Consumer-level averages therefore require grouping multiple bill rows under the same `CAN`.
+### Important Keys and Business Columns
+- **Consumer account identifier:** `CAN`
+- **Consumer name fields:** `FIRSTNAME`, `MIDDLENAME`, `LASTNAME`
+- **Bill amount field used for this prompt:** `NETAMOUNT`
+- **Bill date:** `BILLDATE`
+- **Bill identifier:** `BILLNO`
+### Relationships
+- No extra join is required because the billing/history view already contains both the consumer fields and the billed-amount field needed for the answer.
+### Lookup / Code Mappings
+- No separate lookup table is required.
+- `NETAMOUNT` is used as the bill amount measure for consumer-level averaging.
+### Date Semantics
+- For **?in 2023?**, use a full-year half-open filter on `BILLDATE`:
+  - `&gt;= TIMESTAMP '2023-01-01 00:00:00'`
+  - `&lt; TIMESTAMP '2024-01-01 00:00:00'`
+- The accessible billing snapshot spans `2025-01-01` through `2025-06-30`, so 2023 has no overlap with the available data.
+### Normalization Rules
+- Group by `CAN` for consumer-level averaging.
+- Use name fields only as descriptive context, not as the grouping key.
+- Use `AVG(NETAMOUNT)` as average bill amount per bill row for each consumer.
+### Aggregation Rules
+- Interpret **?average bill amount per consumer?** as:
+  - group by `CAN`
+  - compute `AVG(NETAMOUNT)` across that consumer?s bill rows
+- Safe pattern for this question:
+  - filter by `BILLDATE` for calendar year 2023
+  - group by `CAN`
+  - compute `COUNT(*)` as bill rows
+  - compute `AVG(NETAMOUNT)` as average bill amount per bill
+  - optionally compute `SUM(NETAMOUNT)` as total billed amount
+### Data Quality Notes
+- The accessible billing snapshot contains no 2023 rows.
+- Therefore the consumer-level average-bill result is empty because of source coverage, not because consumers necessarily had zero billed amount in the live business period.
+### Prompt-to-SQL Pattern
+- Typical user phrasing:
+  - ?Show the average bill amount per consumer in 2023.?
+  - ?consumer-wise average bill amount for 2023?
+  - ?average billed amount by consumer for a year?
+- Expected output type:
+  - consumer-level grouped summary when the year exists
+  - explicit no-data statement when the year is outside the accessible snapshot
+### Output Contract
+- Return:
+  - Consumer account
+  - optional consumer name fields
+  - Bill Rows
+  - Average Bill Amount
+  - optionally Total Billed Amount
+### Confidence / Evidence
+- Source confidence: **high**
+- Reason: the billing view directly exposes the consumer and billed-amount fields needed, and the no-data outcome is fully explained by the snapshot date range.</t>
+        </is>
+      </c>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>## SQL Details
+**Discovery Queries**
+None used for this question.
+Reason: the canonical billing/history source and the consumer / billed-amount fields were already established in earlier closely related billing runs.
+**Lookup / Relationship Queries**
+```sql
+select count(*) as bill_rows_2023,
+       count(distinct can) as billed_cans_2023,
+       avg(netamount) as avg_bill_amount_2023,
+       min(billdate) as min_billdate_in_window,
+       max(billdate) as max_billdate_in_window
+from mv_billing_payment_history
+where billdate &gt;= timestamp '2023-01-01 00:00:00'
+  and billdate &lt; timestamp '2024-01-01 00:00:00';
+```
+**Final Business Queries**
+```sql
+select can,
+       max(firstname) as firstname,
+       max(middlename) as middlename,
+       max(lastname) as lastname,
+       count(*) as bill_rows,
+       avg(netamount) as avg_bill_amount_per_bill,
+       sum(netamount) as total_billed_amount
+from mv_billing_payment_history
+where billdate &gt;= timestamp '2023-01-01 00:00:00'
+  and billdate &lt; timestamp '2024-01-01 00:00:00'
+group by can
+order by avg_bill_amount_per_bill desc nulls last, can;
+```</t>
+        </is>
+      </c>
+      <c r="H126" s="12" t="inlineStr">
+        <is>
+          <t>10:50:59.332 - 10:51:23.000 (23.67s)</t>
+        </is>
+      </c>
+      <c r="I126" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H5"/>

--- a/Caddie POC - Result Validation.xlsx
+++ b/Caddie POC - Result Validation.xlsx
@@ -13727,7 +13727,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -13844,10 +13844,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -14266,7 +14263,7 @@
       <c r="B2" s="8">
         <v>1</v>
       </c>
-      <c r="C2" s="44" t="s">
+      <c r="C2" s="8" t="s">
         <v>47</v>
       </c>
       <c r="D2" s="25"/>
@@ -14291,7 +14288,7 @@
       <c r="B3" s="8">
         <v>2</v>
       </c>
-      <c r="C3" s="45" t="s">
+      <c r="C3" s="44" t="s">
         <v>52</v>
       </c>
       <c r="D3" s="9"/>
@@ -14310,7 +14307,7 @@
       <c r="B4" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="45" t="s">
+      <c r="C4" s="44" t="s">
         <v>55</v>
       </c>
       <c r="D4" s="9"/>
@@ -14327,7 +14324,7 @@
       <c r="B5" s="8">
         <v>3</v>
       </c>
-      <c r="C5" s="44" t="s">
+      <c r="C5" s="8" t="s">
         <v>56</v>
       </c>
       <c r="D5" s="9" t="e">
@@ -14357,7 +14354,7 @@
       <c r="B6" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="8" t="s">
         <v>63</v>
       </c>
       <c r="D6" s="9" t="e">
@@ -14385,7 +14382,7 @@
       <c r="B7" s="8">
         <v>5</v>
       </c>
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="8" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="9" t="e">
@@ -14410,7 +14407,7 @@
       <c r="B8" s="8">
         <v>6</v>
       </c>
-      <c r="C8" s="44" t="s">
+      <c r="C8" s="8" t="s">
         <v>71</v>
       </c>
       <c r="D8" s="9" t="e">
@@ -14437,7 +14434,7 @@
       <c r="B9" s="8">
         <v>7</v>
       </c>
-      <c r="C9" s="44" t="s">
+      <c r="C9" s="8" t="s">
         <v>75</v>
       </c>
       <c r="D9" s="9" t="s">
@@ -14456,7 +14453,7 @@
       <c r="B10" s="8">
         <v>8</v>
       </c>
-      <c r="C10" s="44" t="s">
+      <c r="C10" s="8" t="s">
         <v>77</v>
       </c>
       <c r="D10" s="9" t="s">
@@ -14483,7 +14480,7 @@
       <c r="B11" s="8">
         <v>11</v>
       </c>
-      <c r="C11" s="44" t="s">
+      <c r="C11" s="8" t="s">
         <v>82</v>
       </c>
       <c r="D11" s="6" t="s">
@@ -14510,7 +14507,7 @@
       <c r="B12" s="8">
         <v>13</v>
       </c>
-      <c r="C12" s="44" t="s">
+      <c r="C12" s="8" t="s">
         <v>87</v>
       </c>
       <c r="D12" s="6" t="s">
@@ -14535,7 +14532,7 @@
       <c r="B13" s="8">
         <v>17</v>
       </c>
-      <c r="C13" s="44" t="s">
+      <c r="C13" s="8" t="s">
         <v>91</v>
       </c>
       <c r="D13" s="6" t="s">
@@ -14562,7 +14559,7 @@
       <c r="B14" s="8">
         <v>18</v>
       </c>
-      <c r="C14" s="44" t="s">
+      <c r="C14" s="8" t="s">
         <v>96</v>
       </c>
       <c r="D14" s="6" t="s">
@@ -14587,7 +14584,7 @@
       <c r="B15" s="8">
         <v>21</v>
       </c>
-      <c r="C15" s="44" t="s">
+      <c r="C15" s="8" t="s">
         <v>100</v>
       </c>
       <c r="D15" s="6" t="s">
@@ -14606,7 +14603,7 @@
       <c r="B16" s="8">
         <v>25</v>
       </c>
-      <c r="C16" s="44" t="s">
+      <c r="C16" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D16" s="6" t="s">
@@ -14635,7 +14632,7 @@
       <c r="B17" s="8">
         <v>26</v>
       </c>
-      <c r="C17" s="44" t="s">
+      <c r="C17" s="8" t="s">
         <v>108</v>
       </c>
       <c r="D17" s="6" t="s">
@@ -14660,7 +14657,7 @@
       <c r="B18" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="C18" s="44" t="s">
+      <c r="C18" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D18" s="6" t="s">
@@ -14687,7 +14684,7 @@
       <c r="B19" s="8">
         <v>27</v>
       </c>
-      <c r="C19" s="44" t="s">
+      <c r="C19" s="8" t="s">
         <v>13</v>
       </c>
       <c r="D19" s="6" t="s">
@@ -14719,7 +14716,7 @@
       <c r="B20" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="C20" s="44" t="s">
+      <c r="C20" s="8" t="s">
         <v>126</v>
       </c>
       <c r="D20" s="6" t="s">
@@ -14746,7 +14743,7 @@
       <c r="B21" s="8">
         <v>28</v>
       </c>
-      <c r="C21" s="44" t="s">
+      <c r="C21" s="8" t="s">
         <v>131</v>
       </c>
       <c r="D21" s="6" t="s">
@@ -14775,7 +14772,7 @@
       <c r="B22" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="C22" s="44" t="s">
+      <c r="C22" s="8" t="s">
         <v>138</v>
       </c>
       <c r="D22" s="6" t="s">
@@ -14802,7 +14799,7 @@
       <c r="B23" s="8">
         <v>29</v>
       </c>
-      <c r="C23" s="44" t="s">
+      <c r="C23" s="8" t="s">
         <v>143</v>
       </c>
       <c r="D23" s="6" t="s">
@@ -14829,7 +14826,7 @@
       <c r="B24" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="C24" s="44" t="s">
+      <c r="C24" s="8" t="s">
         <v>149</v>
       </c>
       <c r="D24" s="14" t="s">
@@ -14856,7 +14853,7 @@
       <c r="B25" s="8">
         <v>30</v>
       </c>
-      <c r="C25" s="44" t="s">
+      <c r="C25" s="8" t="s">
         <v>153</v>
       </c>
       <c r="D25" s="26" t="s">
@@ -14877,7 +14874,7 @@
       <c r="B26" s="8">
         <v>31</v>
       </c>
-      <c r="C26" s="44" t="s">
+      <c r="C26" s="8" t="s">
         <v>17</v>
       </c>
       <c r="D26" s="14" t="s">
@@ -14906,7 +14903,7 @@
       <c r="B27" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="44" t="s">
+      <c r="C27" s="8" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="14" t="s">
@@ -14935,7 +14932,7 @@
       <c r="B28" s="8">
         <v>32</v>
       </c>
-      <c r="C28" s="44" t="s">
+      <c r="C28" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D28" s="14" t="s">
@@ -14964,7 +14961,7 @@
       <c r="B29" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C29" s="44" t="s">
+      <c r="C29" s="8" t="s">
         <v>31</v>
       </c>
       <c r="D29" s="15" t="s">
@@ -14993,7 +14990,7 @@
       <c r="B30" s="8">
         <v>34</v>
       </c>
-      <c r="C30" s="44" t="s">
+      <c r="C30" s="8" t="s">
         <v>173</v>
       </c>
       <c r="D30" s="15" t="s">
@@ -15022,7 +15019,7 @@
       <c r="B31" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="C31" s="44" t="s">
+      <c r="C31" s="8" t="s">
         <v>179</v>
       </c>
       <c r="D31" s="15" t="s">
@@ -15051,7 +15048,7 @@
       <c r="B32" s="8">
         <v>38</v>
       </c>
-      <c r="C32" s="44" t="s">
+      <c r="C32" s="8" t="s">
         <v>184</v>
       </c>
       <c r="D32" s="15" t="s">
@@ -15080,7 +15077,7 @@
       <c r="B33" s="8">
         <v>43</v>
       </c>
-      <c r="C33" s="44" t="s">
+      <c r="C33" s="8" t="s">
         <v>35</v>
       </c>
       <c r="D33" s="15" t="s">
@@ -15109,7 +15106,7 @@
       <c r="B34" s="8">
         <v>44</v>
       </c>
-      <c r="C34" s="44" t="s">
+      <c r="C34" s="8" t="s">
         <v>193</v>
       </c>
       <c r="D34" s="15" t="s">
@@ -15138,7 +15135,7 @@
       <c r="B35" s="8">
         <v>46</v>
       </c>
-      <c r="C35" s="44" t="s">
+      <c r="C35" s="8" t="s">
         <v>39</v>
       </c>
       <c r="D35" s="15" t="s">
@@ -15167,7 +15164,7 @@
       <c r="B36" s="8">
         <v>47</v>
       </c>
-      <c r="C36" s="44" t="s">
+      <c r="C36" s="8" t="s">
         <v>204</v>
       </c>
       <c r="D36" s="15" t="s">
@@ -15196,7 +15193,7 @@
       <c r="B37" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="C37" s="44" t="s">
+      <c r="C37" s="8" t="s">
         <v>211</v>
       </c>
       <c r="D37" s="15" t="s">
@@ -15223,7 +15220,7 @@
       <c r="B38" s="8">
         <v>48</v>
       </c>
-      <c r="C38" s="44" t="s">
+      <c r="C38" s="8" t="s">
         <v>43</v>
       </c>
       <c r="D38" s="15" t="s">
@@ -15252,7 +15249,7 @@
       <c r="B39" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="C39" s="44" t="s">
+      <c r="C39" s="8" t="s">
         <v>222</v>
       </c>
       <c r="D39" s="15" t="s">
@@ -15281,7 +15278,7 @@
       <c r="B40" s="8">
         <v>50</v>
       </c>
-      <c r="C40" s="44" t="s">
+      <c r="C40" s="8" t="s">
         <v>227</v>
       </c>
       <c r="D40" s="14" t="s">
@@ -15310,7 +15307,7 @@
       <c r="B41" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="C41" s="44" t="s">
+      <c r="C41" s="8" t="s">
         <v>234</v>
       </c>
       <c r="D41" s="15" t="s">
@@ -15339,7 +15336,7 @@
       <c r="B42" s="8">
         <v>51</v>
       </c>
-      <c r="C42" s="44" t="s">
+      <c r="C42" s="8" t="s">
         <v>239</v>
       </c>
       <c r="D42" s="15" t="s">
@@ -15369,7 +15366,7 @@
       <c r="B43" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="C43" s="44" t="s">
+      <c r="C43" s="8" t="s">
         <v>247</v>
       </c>
       <c r="D43" s="15" t="s">
@@ -15396,7 +15393,7 @@
       <c r="B44" s="8">
         <v>52</v>
       </c>
-      <c r="C44" s="44" t="s">
+      <c r="C44" s="8" t="s">
         <v>252</v>
       </c>
       <c r="D44" s="15" t="s">
@@ -15423,7 +15420,7 @@
       <c r="B45" s="8">
         <v>53</v>
       </c>
-      <c r="C45" s="44" t="s">
+      <c r="C45" s="8" t="s">
         <v>258</v>
       </c>
       <c r="D45" s="15" t="s">
@@ -15450,7 +15447,7 @@
       <c r="B46" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="C46" s="44" t="s">
+      <c r="C46" s="8" t="s">
         <v>265</v>
       </c>
       <c r="D46" s="15" t="s">
@@ -15477,7 +15474,7 @@
       <c r="B47" s="8">
         <v>54</v>
       </c>
-      <c r="C47" s="44" t="s">
+      <c r="C47" s="8" t="s">
         <v>270</v>
       </c>
       <c r="D47" s="15" t="s">
@@ -15504,7 +15501,7 @@
       <c r="B48" s="8">
         <v>55</v>
       </c>
-      <c r="C48" s="44" t="s">
+      <c r="C48" s="8" t="s">
         <v>275</v>
       </c>
       <c r="D48" s="15" t="s">
@@ -15531,7 +15528,7 @@
       <c r="B49" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="C49" s="44" t="s">
+      <c r="C49" s="8" t="s">
         <v>282</v>
       </c>
       <c r="D49" s="15" t="s">
@@ -15558,7 +15555,7 @@
       <c r="B50" s="8">
         <v>60</v>
       </c>
-      <c r="C50" s="44" t="s">
+      <c r="C50" s="8" t="s">
         <v>287</v>
       </c>
       <c r="D50" s="15" t="s">
@@ -15585,7 +15582,7 @@
       <c r="B51" s="8">
         <v>62</v>
       </c>
-      <c r="C51" s="44" t="s">
+      <c r="C51" s="8" t="s">
         <v>292</v>
       </c>
       <c r="D51" s="15" t="s">
@@ -15612,7 +15609,7 @@
       <c r="B52" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="C52" s="44" t="s">
+      <c r="C52" s="8" t="s">
         <v>299</v>
       </c>
       <c r="D52" s="15" t="s">
@@ -15639,7 +15636,7 @@
       <c r="B53" s="8">
         <v>63</v>
       </c>
-      <c r="C53" s="44" t="s">
+      <c r="C53" s="8" t="s">
         <v>304</v>
       </c>
       <c r="D53" s="15" t="s">
@@ -15666,7 +15663,7 @@
       <c r="B54" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="C54" s="44" t="s">
+      <c r="C54" s="8" t="s">
         <v>310</v>
       </c>
       <c r="D54" s="15" t="s">
@@ -15693,7 +15690,7 @@
       <c r="B55" s="8">
         <v>64</v>
       </c>
-      <c r="C55" s="44" t="s">
+      <c r="C55" s="8" t="s">
         <v>315</v>
       </c>
       <c r="D55" s="15" t="s">
@@ -15720,7 +15717,7 @@
       <c r="B56" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="C56" s="44" t="s">
+      <c r="C56" s="8" t="s">
         <v>321</v>
       </c>
       <c r="D56" s="15" t="s">
@@ -15747,7 +15744,7 @@
       <c r="B57" s="8">
         <v>65</v>
       </c>
-      <c r="C57" s="44" t="s">
+      <c r="C57" s="8" t="s">
         <v>326</v>
       </c>
       <c r="D57" s="15" t="s">
@@ -15774,7 +15771,7 @@
       <c r="B58" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="C58" s="44" t="s">
+      <c r="C58" s="8" t="s">
         <v>332</v>
       </c>
       <c r="D58" s="15" t="s">
@@ -15801,7 +15798,7 @@
       <c r="B59" s="8">
         <v>66</v>
       </c>
-      <c r="C59" s="44" t="s">
+      <c r="C59" s="8" t="s">
         <v>337</v>
       </c>
       <c r="D59" s="15" t="s">
@@ -15828,7 +15825,7 @@
       <c r="B60" s="8">
         <v>67</v>
       </c>
-      <c r="C60" s="44" t="s">
+      <c r="C60" s="8" t="s">
         <v>342</v>
       </c>
       <c r="D60" s="15" t="s">
@@ -15855,7 +15852,7 @@
       <c r="B61" s="8">
         <v>68</v>
       </c>
-      <c r="C61" s="44" t="s">
+      <c r="C61" s="8" t="s">
         <v>347</v>
       </c>
       <c r="D61" s="15" t="s">
@@ -15882,7 +15879,7 @@
       <c r="B62" s="8">
         <v>69</v>
       </c>
-      <c r="C62" s="44" t="s">
+      <c r="C62" s="8" t="s">
         <v>352</v>
       </c>
       <c r="D62" s="15" t="s">
@@ -15909,7 +15906,7 @@
       <c r="B63" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="C63" s="44" t="s">
+      <c r="C63" s="8" t="s">
         <v>359</v>
       </c>
       <c r="D63" s="15" t="s">
@@ -15936,7 +15933,7 @@
       <c r="B64" s="8">
         <v>70</v>
       </c>
-      <c r="C64" s="44" t="s">
+      <c r="C64" s="8" t="s">
         <v>364</v>
       </c>
       <c r="D64" s="14" t="s">
@@ -15963,7 +15960,7 @@
       <c r="B65" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="C65" s="44" t="s">
+      <c r="C65" s="8" t="s">
         <v>371</v>
       </c>
       <c r="D65" s="15" t="s">
@@ -15990,7 +15987,7 @@
       <c r="B66" s="8">
         <v>71</v>
       </c>
-      <c r="C66" s="44" t="s">
+      <c r="C66" s="8" t="s">
         <v>376</v>
       </c>
       <c r="D66" s="15" t="s">
@@ -16017,7 +16014,7 @@
       <c r="B67" s="8">
         <v>72</v>
       </c>
-      <c r="C67" s="44" t="s">
+      <c r="C67" s="8" t="s">
         <v>382</v>
       </c>
       <c r="D67" s="15" t="s">
@@ -16044,7 +16041,7 @@
       <c r="B68" s="8" t="s">
         <v>388</v>
       </c>
-      <c r="C68" s="44" t="s">
+      <c r="C68" s="8" t="s">
         <v>389</v>
       </c>
       <c r="D68" s="15" t="s">
@@ -16071,7 +16068,7 @@
       <c r="B69" s="8">
         <v>73</v>
       </c>
-      <c r="C69" s="44" t="s">
+      <c r="C69" s="8" t="s">
         <v>394</v>
       </c>
       <c r="D69" s="15" t="s">
@@ -16098,7 +16095,7 @@
       <c r="B70" s="8">
         <v>74</v>
       </c>
-      <c r="C70" s="44" t="s">
+      <c r="C70" s="8" t="s">
         <v>399</v>
       </c>
       <c r="D70" s="15" t="s">
@@ -16125,7 +16122,7 @@
       <c r="B71" s="8">
         <v>75</v>
       </c>
-      <c r="C71" s="44" t="s">
+      <c r="C71" s="8" t="s">
         <v>404</v>
       </c>
       <c r="D71" s="15" t="s">
@@ -16152,7 +16149,7 @@
       <c r="B72" s="8">
         <v>76</v>
       </c>
-      <c r="C72" s="44" t="s">
+      <c r="C72" s="8" t="s">
         <v>409</v>
       </c>
       <c r="D72" s="14" t="s">
@@ -16179,7 +16176,7 @@
       <c r="B73" s="8">
         <v>77</v>
       </c>
-      <c r="C73" s="44" t="s">
+      <c r="C73" s="8" t="s">
         <v>414</v>
       </c>
       <c r="D73" s="15" t="s">
@@ -16206,7 +16203,7 @@
       <c r="B74" s="8">
         <v>78</v>
       </c>
-      <c r="C74" s="44" t="s">
+      <c r="C74" s="8" t="s">
         <v>420</v>
       </c>
       <c r="D74" s="15" t="s">
@@ -16233,7 +16230,7 @@
       <c r="B75" s="8">
         <v>79</v>
       </c>
-      <c r="C75" s="44" t="s">
+      <c r="C75" s="8" t="s">
         <v>425</v>
       </c>
       <c r="D75" s="15" t="s">
@@ -16260,7 +16257,7 @@
       <c r="B76" s="8">
         <v>246</v>
       </c>
-      <c r="C76" s="44" t="s">
+      <c r="C76" s="8" t="s">
         <v>430</v>
       </c>
       <c r="D76" s="15" t="s">
@@ -16287,7 +16284,7 @@
       <c r="B77" s="8">
         <v>247</v>
       </c>
-      <c r="C77" s="44" t="s">
+      <c r="C77" s="8" t="s">
         <v>435</v>
       </c>
       <c r="D77" s="15" t="s">
@@ -16314,7 +16311,7 @@
       <c r="B78" s="8">
         <v>248</v>
       </c>
-      <c r="C78" s="44" t="s">
+      <c r="C78" s="8" t="s">
         <v>440</v>
       </c>
       <c r="D78" s="15" t="s">
@@ -16341,7 +16338,7 @@
       <c r="B79" s="8" t="s">
         <v>445</v>
       </c>
-      <c r="C79" s="44" t="s">
+      <c r="C79" s="8" t="s">
         <v>446</v>
       </c>
       <c r="D79" s="15" t="s">
@@ -16368,7 +16365,7 @@
       <c r="B80" s="8">
         <v>249</v>
       </c>
-      <c r="C80" s="44" t="s">
+      <c r="C80" s="8" t="s">
         <v>451</v>
       </c>
       <c r="D80" s="15" t="s">
@@ -16395,7 +16392,7 @@
       <c r="B81" s="8" t="s">
         <v>456</v>
       </c>
-      <c r="C81" s="44" t="s">
+      <c r="C81" s="8" t="s">
         <v>457</v>
       </c>
       <c r="D81" s="15" t="s">
@@ -16422,7 +16419,7 @@
       <c r="B82" s="8">
         <v>250</v>
       </c>
-      <c r="C82" s="44" t="s">
+      <c r="C82" s="8" t="s">
         <v>462</v>
       </c>
       <c r="D82" s="14" t="s">
@@ -16451,7 +16448,7 @@
       <c r="B83" s="8">
         <v>253</v>
       </c>
-      <c r="C83" s="44" t="s">
+      <c r="C83" s="8" t="s">
         <v>467</v>
       </c>
       <c r="D83" s="15" t="s">
@@ -16480,7 +16477,7 @@
       <c r="B84" s="8" t="s">
         <v>472</v>
       </c>
-      <c r="C84" s="44" t="s">
+      <c r="C84" s="8" t="s">
         <v>473</v>
       </c>
       <c r="D84" s="15" t="s">
@@ -16509,7 +16506,7 @@
       <c r="B85" s="8">
         <v>254</v>
       </c>
-      <c r="C85" s="44" t="s">
+      <c r="C85" s="8" t="s">
         <v>478</v>
       </c>
       <c r="D85" s="15" t="s">
@@ -16538,7 +16535,7 @@
       <c r="B86" s="8" t="s">
         <v>483</v>
       </c>
-      <c r="C86" s="44" t="s">
+      <c r="C86" s="8" t="s">
         <v>484</v>
       </c>
       <c r="D86" s="15" t="s">
@@ -16567,7 +16564,7 @@
       <c r="B87" s="8">
         <v>256</v>
       </c>
-      <c r="C87" s="44" t="s">
+      <c r="C87" s="8" t="s">
         <v>489</v>
       </c>
       <c r="D87" s="15" t="s">
@@ -16596,7 +16593,7 @@
       <c r="B88" s="8">
         <v>257</v>
       </c>
-      <c r="C88" s="44" t="s">
+      <c r="C88" s="8" t="s">
         <v>494</v>
       </c>
       <c r="D88" s="15" t="s">
@@ -16625,7 +16622,7 @@
       <c r="B89" s="8">
         <v>258</v>
       </c>
-      <c r="C89" s="44" t="s">
+      <c r="C89" s="8" t="s">
         <v>499</v>
       </c>
       <c r="D89" s="15" t="s">
@@ -16654,7 +16651,7 @@
       <c r="B90" s="8">
         <v>259</v>
       </c>
-      <c r="C90" s="44" t="s">
+      <c r="C90" s="8" t="s">
         <v>504</v>
       </c>
       <c r="D90" s="15" t="s">
@@ -16683,7 +16680,7 @@
       <c r="B91" s="8">
         <v>260</v>
       </c>
-      <c r="C91" s="44" t="s">
+      <c r="C91" s="8" t="s">
         <v>509</v>
       </c>
       <c r="D91" s="15" t="s">
@@ -16712,7 +16709,7 @@
       <c r="B92" s="8">
         <v>261</v>
       </c>
-      <c r="C92" s="44" t="s">
+      <c r="C92" s="8" t="s">
         <v>514</v>
       </c>
       <c r="D92" s="15" t="s">
@@ -16741,7 +16738,7 @@
       <c r="B93" s="8">
         <v>262</v>
       </c>
-      <c r="C93" s="44" t="s">
+      <c r="C93" s="8" t="s">
         <v>519</v>
       </c>
       <c r="D93" s="14" t="s">
@@ -16771,7 +16768,7 @@
       <c r="B94" s="8">
         <v>263</v>
       </c>
-      <c r="C94" s="44" t="s">
+      <c r="C94" s="8" t="s">
         <v>524</v>
       </c>
       <c r="D94" s="15" t="s">
@@ -16801,7 +16798,7 @@
       <c r="B95" s="8">
         <v>264</v>
       </c>
-      <c r="C95" s="44" t="s">
+      <c r="C95" s="8" t="s">
         <v>529</v>
       </c>
       <c r="D95" s="15" t="s">
@@ -16831,7 +16828,7 @@
       <c r="B96" s="8" t="s">
         <v>534</v>
       </c>
-      <c r="C96" s="44" t="s">
+      <c r="C96" s="8" t="s">
         <v>535</v>
       </c>
       <c r="D96" s="15" t="s">
@@ -16861,7 +16858,7 @@
       <c r="B97" s="8">
         <v>265</v>
       </c>
-      <c r="C97" s="44" t="s">
+      <c r="C97" s="8" t="s">
         <v>540</v>
       </c>
       <c r="D97" s="15" t="s">
@@ -16891,7 +16888,7 @@
       <c r="B98" s="8">
         <v>266</v>
       </c>
-      <c r="C98" s="44" t="s">
+      <c r="C98" s="8" t="s">
         <v>545</v>
       </c>
       <c r="D98" s="15" t="s">
@@ -16921,7 +16918,7 @@
       <c r="B99" s="8">
         <v>267</v>
       </c>
-      <c r="C99" s="44" t="s">
+      <c r="C99" s="8" t="s">
         <v>550</v>
       </c>
       <c r="D99" s="15" t="s">
@@ -16951,7 +16948,7 @@
       <c r="B100" s="8">
         <v>268</v>
       </c>
-      <c r="C100" s="44" t="s">
+      <c r="C100" s="8" t="s">
         <v>555</v>
       </c>
       <c r="D100" s="15" t="s">
@@ -16981,7 +16978,7 @@
       <c r="B101" s="8">
         <v>269</v>
       </c>
-      <c r="C101" s="44" t="s">
+      <c r="C101" s="8" t="s">
         <v>560</v>
       </c>
       <c r="D101" s="14" t="s">
@@ -17011,7 +17008,7 @@
       <c r="B102" s="8">
         <v>270</v>
       </c>
-      <c r="C102" s="44" t="s">
+      <c r="C102" s="8" t="s">
         <v>565</v>
       </c>
       <c r="D102" s="15" t="s">
@@ -17041,7 +17038,7 @@
       <c r="B103" s="8">
         <v>271</v>
       </c>
-      <c r="C103" s="44" t="s">
+      <c r="C103" s="8" t="s">
         <v>570</v>
       </c>
       <c r="D103" s="15" t="s">
@@ -17071,7 +17068,7 @@
       <c r="B104" s="8">
         <v>272</v>
       </c>
-      <c r="C104" s="44" t="s">
+      <c r="C104" s="8" t="s">
         <v>576</v>
       </c>
       <c r="D104" s="15" t="s">
@@ -17101,7 +17098,7 @@
       <c r="B105" s="8">
         <v>273</v>
       </c>
-      <c r="C105" s="44" t="s">
+      <c r="C105" s="8" t="s">
         <v>581</v>
       </c>
       <c r="D105" s="20" t="s">
@@ -17131,7 +17128,7 @@
       <c r="B106" s="8">
         <v>274</v>
       </c>
-      <c r="C106" s="44" t="s">
+      <c r="C106" s="8" t="s">
         <v>586</v>
       </c>
       <c r="D106" s="20" t="s">
@@ -17163,7 +17160,7 @@
       <c r="B107" s="8">
         <v>275</v>
       </c>
-      <c r="C107" s="44" t="s">
+      <c r="C107" s="8" t="s">
         <v>591</v>
       </c>
       <c r="D107" s="20" t="s">
@@ -17194,7 +17191,7 @@
       <c r="B108" s="8">
         <v>276</v>
       </c>
-      <c r="C108" s="44" t="s">
+      <c r="C108" s="8" t="s">
         <v>596</v>
       </c>
       <c r="D108" s="22" t="s">
@@ -17224,7 +17221,7 @@
       <c r="B109" s="8">
         <v>277</v>
       </c>
-      <c r="C109" s="44" t="s">
+      <c r="C109" s="8" t="s">
         <v>601</v>
       </c>
       <c r="D109" s="22" t="s">
@@ -17254,7 +17251,7 @@
       <c r="B110" s="8">
         <v>278</v>
       </c>
-      <c r="C110" s="44" t="s">
+      <c r="C110" s="8" t="s">
         <v>606</v>
       </c>
       <c r="D110" s="22" t="s">
@@ -17284,7 +17281,7 @@
       <c r="B111" s="8">
         <v>283</v>
       </c>
-      <c r="C111" s="44" t="s">
+      <c r="C111" s="8" t="s">
         <v>611</v>
       </c>
       <c r="D111" s="22" t="s">
@@ -17314,7 +17311,7 @@
       <c r="B112" s="8">
         <v>284</v>
       </c>
-      <c r="C112" s="44" t="s">
+      <c r="C112" s="8" t="s">
         <v>616</v>
       </c>
       <c r="D112" s="22" t="s">
@@ -17344,7 +17341,7 @@
       <c r="B113" s="8" t="s">
         <v>621</v>
       </c>
-      <c r="C113" s="44" t="s">
+      <c r="C113" s="8" t="s">
         <v>622</v>
       </c>
       <c r="D113" s="20" t="s">
@@ -17374,7 +17371,7 @@
       <c r="B114" s="8">
         <v>285</v>
       </c>
-      <c r="C114" s="44" t="s">
+      <c r="C114" s="8" t="s">
         <v>627</v>
       </c>
       <c r="D114" s="15" t="s">
@@ -17404,7 +17401,7 @@
       <c r="B115" s="8">
         <v>286</v>
       </c>
-      <c r="C115" s="44" t="s">
+      <c r="C115" s="8" t="s">
         <v>633</v>
       </c>
       <c r="D115" s="15" t="s">
@@ -17434,7 +17431,7 @@
       <c r="B116" s="8">
         <v>287</v>
       </c>
-      <c r="C116" s="44" t="s">
+      <c r="C116" s="8" t="s">
         <v>638</v>
       </c>
       <c r="D116" s="15" t="s">
@@ -17464,7 +17461,7 @@
       <c r="B117" s="8">
         <v>288</v>
       </c>
-      <c r="C117" s="44" t="s">
+      <c r="C117" s="8" t="s">
         <v>643</v>
       </c>
       <c r="D117" s="15" t="s">
@@ -17494,7 +17491,7 @@
       <c r="B118" s="8">
         <v>289</v>
       </c>
-      <c r="C118" s="44" t="s">
+      <c r="C118" s="8" t="s">
         <v>648</v>
       </c>
       <c r="D118" s="15" t="s">
@@ -17524,7 +17521,7 @@
       <c r="B119" s="8">
         <v>290</v>
       </c>
-      <c r="C119" s="44" t="s">
+      <c r="C119" s="8" t="s">
         <v>653</v>
       </c>
       <c r="D119" s="15" t="s">
@@ -17554,7 +17551,7 @@
       <c r="B120" s="8">
         <v>291</v>
       </c>
-      <c r="C120" s="44" t="s">
+      <c r="C120" s="8" t="s">
         <v>659</v>
       </c>
       <c r="D120" s="6" t="s">
@@ -17581,7 +17578,7 @@
       <c r="B121" s="8">
         <v>292</v>
       </c>
-      <c r="C121" s="44" t="s">
+      <c r="C121" s="8" t="s">
         <v>664</v>
       </c>
       <c r="D121" s="6" t="s">
@@ -17608,7 +17605,7 @@
       <c r="B122" s="8">
         <v>293</v>
       </c>
-      <c r="C122" s="44" t="s">
+      <c r="C122" s="8" t="s">
         <v>669</v>
       </c>
       <c r="D122" s="6" t="s">
@@ -17635,7 +17632,7 @@
       <c r="B123" s="8">
         <v>294</v>
       </c>
-      <c r="C123" s="44" t="s">
+      <c r="C123" s="8" t="s">
         <v>674</v>
       </c>
       <c r="D123" s="6" t="s">
@@ -17662,7 +17659,7 @@
       <c r="B124" s="8" t="s">
         <v>680</v>
       </c>
-      <c r="C124" s="44" t="s">
+      <c r="C124" s="8" t="s">
         <v>681</v>
       </c>
       <c r="D124" s="6" t="s">
@@ -17689,7 +17686,7 @@
       <c r="B125" s="8">
         <v>296</v>
       </c>
-      <c r="C125" s="44" t="s">
+      <c r="C125" s="8" t="s">
         <v>686</v>
       </c>
       <c r="D125" s="6" t="s">
@@ -17716,7 +17713,7 @@
       <c r="B126" s="8">
         <v>298</v>
       </c>
-      <c r="C126" s="44" t="s">
+      <c r="C126" s="8" t="s">
         <v>691</v>
       </c>
       <c r="D126" s="6" t="s">
